--- a/data/trans_orig/IP24_2023-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Dificultad-trans_orig.xlsx
@@ -1007,7 +1007,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1508,7 +1508,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2009,7 +2009,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2510,7 +2510,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -3011,7 +3011,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
